--- a/output/CLOTH01_summer/feeds_excel/master data feeds/ItemMaster.xlsx
+++ b/output/CLOTH01_summer/feeds_excel/master data feeds/ItemMaster.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,233 +466,45 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ITM_BAS_0001</t>
+          <t>ITM_CHIPS_8OZ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Black Basics XS (BSC_001)</t>
+          <t>Potato Chips 8oz</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>EXT-ITM_BAS_0001</t>
+          <t>EXT-ITM_CHIPS_8OZ</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>XS</t>
+          <t>One Size</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Alpha</t>
+          <t>Pack</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>BSC_001</t>
+          <t>SNK_001</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Black</t>
+          <t>Yellow</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>BSC_001-BLA-XS</t>
+          <t>SNK_001-YEL-One Size</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>ITM_BAS_0002</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>White Basics S (BSC_002)</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>EXT-ITM_BAS_0002</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Alpha</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>BSC_002</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>White</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>BSC_002-WHI-S</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>ITM_TOP_0003</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Black Tops XS (TOP_001)</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>EXT-ITM_TOP_0003</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>XS</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Alpha</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>TOP_001</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Black</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>TOP_001-BLA-XS</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>ITM_TOP_0004</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>White Tops S (TOP_002)</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>EXT-ITM_TOP_0004</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Alpha</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>TOP_002</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>White</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>TOP_002-WHI-S</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>ITM_BOT_0005</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Black Bottoms 28 (BTM_001)</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>EXT-ITM_BOT_0005</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Waist</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>BTM_001</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Black</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>BTM_001-BLA-28</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
